--- a/questionnaire_templates/027_interdisciplinary_learning_barriers_survey--questionnaire_templates.xlsx
+++ b/questionnaire_templates/027_interdisciplinary_learning_barriers_survey--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -987,8 +987,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="43" customWidth="1" min="2" max="2"/>
-    <col width="43" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1016,12 +1016,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'always'}</t>
+          <t>always</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Always'}</t>
+          <t>Always</t>
         </is>
       </c>
     </row>
@@ -1033,12 +1033,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'frequently'}</t>
+          <t>frequently</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Frequently'}</t>
+          <t>Frequently</t>
         </is>
       </c>
     </row>
@@ -1050,12 +1050,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'occasionally'}</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Occasionally'}</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1084,12 +1084,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1101,12 +1101,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'lack_of_clear_goals'}</t>
+          <t>lack_of_clear_goals</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Lack of clear goals'}</t>
+          <t>Lack of clear goals</t>
         </is>
       </c>
     </row>
@@ -1118,12 +1118,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'inadequate_resources'}</t>
+          <t>inadequate_resources</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Inadequate resources'}</t>
+          <t>Inadequate resources</t>
         </is>
       </c>
     </row>
@@ -1135,12 +1135,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'lack_of_support'}</t>
+          <t>lack_of_support</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Lack of support'}</t>
+          <t>Lack of support</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'insufficient_time'}</t>
+          <t>insufficient_time</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Insufficient time'}</t>
+          <t>Insufficient time</t>
         </is>
       </c>
     </row>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'difficulty_with_team_members'}</t>
+          <t>difficulty_with_team_members</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Difficulty with team members'}</t>
+          <t>Difficulty with team members</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1203,12 +1203,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1237,12 +1237,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1254,12 +1254,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'male'}</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Male'}</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'female'}</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Female'}</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1305,12 +1305,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'biology'}</t>
+          <t>biology</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Biology'}</t>
+          <t>Biology</t>
         </is>
       </c>
     </row>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'chemistry'}</t>
+          <t>chemistry</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Chemistry'}</t>
+          <t>Chemistry</t>
         </is>
       </c>
     </row>
@@ -1339,12 +1339,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'physics'}</t>
+          <t>physics</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Physics'}</t>
+          <t>Physics</t>
         </is>
       </c>
     </row>
@@ -1356,12 +1356,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1373,12 +1373,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1407,12 +1407,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'very_likely'}</t>
+          <t>very_likely</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Very likely'}</t>
+          <t>Very likely</t>
         </is>
       </c>
     </row>
@@ -1441,12 +1441,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_likely'}</t>
+          <t>somewhat_likely</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat likely'}</t>
+          <t>Somewhat likely</t>
         </is>
       </c>
     </row>
@@ -1458,12 +1458,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'not_likely'}</t>
+          <t>not_likely</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Not likely'}</t>
+          <t>Not likely</t>
         </is>
       </c>
     </row>
@@ -1475,12 +1475,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'very_unlikely'}</t>
+          <t>very_unlikely</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Very unlikely'}</t>
+          <t>Very unlikely</t>
         </is>
       </c>
     </row>
@@ -1492,12 +1492,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'a_lot'}</t>
+          <t>a_lot</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'A lot'}</t>
+          <t>A lot</t>
         </is>
       </c>
     </row>
@@ -1509,12 +1509,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'a_moderate_amount'}</t>
+          <t>a_moderate_amount</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'A moderate amount'}</t>
+          <t>A moderate amount</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'a_small_amount'}</t>
+          <t>a_small_amount</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'A small amount'}</t>
+          <t>A small amount</t>
         </is>
       </c>
     </row>
@@ -1543,12 +1543,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1560,12 +1560,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1577,12 +1577,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'label':_'highly'}</t>
+          <t>highly</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'label': 'Highly'}</t>
+          <t>Highly</t>
         </is>
       </c>
     </row>
@@ -1594,12 +1594,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat'}</t>
+          <t>somewhat</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat'}</t>
+          <t>Somewhat</t>
         </is>
       </c>
     </row>
@@ -1611,12 +1611,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'label':_'not_at_all'}</t>
+          <t>not_at_all</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'label': 'Not at all'}</t>
+          <t>Not at all</t>
         </is>
       </c>
     </row>
@@ -1628,12 +1628,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'label':_'very'}</t>
+          <t>very</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'label': 'Very'}</t>
+          <t>Very</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat'}</t>
+          <t>somewhat</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat'}</t>
+          <t>Somewhat</t>
         </is>
       </c>
     </row>
@@ -1662,12 +1662,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'label':_'not_very'}</t>
+          <t>not_very</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'label': 'Not very'}</t>
+          <t>Not very</t>
         </is>
       </c>
     </row>
@@ -1679,12 +1679,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'label':_'not_at_all'}</t>
+          <t>not_at_all</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'label': 'Not at all'}</t>
+          <t>Not at all</t>
         </is>
       </c>
     </row>
@@ -1696,12 +1696,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'label':_'a_lot'}</t>
+          <t>a_lot</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'label': 'A lot'}</t>
+          <t>A lot</t>
         </is>
       </c>
     </row>
@@ -1713,12 +1713,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'label':_'a_moderate_amount'}</t>
+          <t>a_moderate_amount</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'label': 'A moderate amount'}</t>
+          <t>A moderate amount</t>
         </is>
       </c>
     </row>
@@ -1730,12 +1730,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'label':_'a_small_amount'}</t>
+          <t>a_small_amount</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'label': 'A small amount'}</t>
+          <t>A small amount</t>
         </is>
       </c>
     </row>
@@ -1747,12 +1747,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1764,12 +1764,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
